--- a/Data/writeoffs.xlsx
+++ b/Data/writeoffs.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/05c776d51af9edc4/Work-related/VS - Code project/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{43C25326-DA3E-4271-B38D-BC3A8A6FB2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79867E53-3742-4213-AF87-E7F15EE7D398}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="13_ncr:1_{43C25326-DA3E-4271-B38D-BC3A8A6FB2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{345D5558-B22D-432F-BEAF-D1C22136F119}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AY28"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
@@ -597,10 +597,10 @@
     <col min="17" max="21" width="15" bestFit="1" customWidth="1"/>
     <col min="22" max="23" width="16" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="13" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -674,7 +674,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>38</v>
       </c>
@@ -773,7 +773,7 @@
       <c r="AX2" s="10"/>
       <c r="AY2" s="10"/>
     </row>
-    <row r="3" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>44</v>
       </c>
@@ -847,7 +847,7 @@
         <v>-101958</v>
       </c>
     </row>
-    <row r="4" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -922,7 +922,7 @@
       </c>
       <c r="Y4" s="11"/>
     </row>
-    <row r="5" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -996,7 +996,7 @@
         <v>-6316176</v>
       </c>
     </row>
-    <row r="6" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>-7796382</v>
       </c>
     </row>
-    <row r="7" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>-3681973</v>
       </c>
     </row>
-    <row r="9" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>-151166</v>
       </c>
     </row>
-    <row r="10" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>-3242440</v>
       </c>
     </row>
-    <row r="11" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>33</v>
       </c>
@@ -1440,7 +1440,7 @@
         <v>-658197</v>
       </c>
     </row>
-    <row r="12" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>43</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>34</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>-417732.27</v>
       </c>
     </row>
-    <row r="14" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>47</v>
       </c>
@@ -1599,62 +1599,62 @@
         <v>0</v>
       </c>
       <c r="D14" s="9">
-        <v>0</v>
+        <v>-935377</v>
       </c>
       <c r="E14" s="9">
         <v>0</v>
       </c>
       <c r="F14" s="9">
-        <v>-2979772</v>
+        <v>-2044395</v>
       </c>
       <c r="G14" s="9">
         <v>0</v>
       </c>
       <c r="H14" s="9">
-        <v>0</v>
+        <v>-1736079</v>
       </c>
       <c r="I14" s="9">
         <v>0</v>
       </c>
       <c r="J14" s="9">
-        <v>-6613784</v>
+        <v>-4877705</v>
       </c>
       <c r="K14" s="9">
         <v>0</v>
       </c>
       <c r="L14" s="9">
-        <v>0</v>
+        <v>-479007</v>
       </c>
       <c r="M14" s="9">
         <v>0</v>
       </c>
       <c r="N14" s="9">
-        <v>-2707852</v>
+        <v>-2228845</v>
       </c>
       <c r="O14" s="9">
         <v>0</v>
       </c>
       <c r="P14" s="9">
-        <v>0</v>
+        <v>-2417255</v>
       </c>
       <c r="Q14" s="9">
         <v>0</v>
       </c>
       <c r="R14" s="9">
-        <f>-4432650-533615</f>
-        <v>-4966265</v>
+        <f>(-4432650-533615)--2417255</f>
+        <v>-2549010</v>
       </c>
       <c r="S14" s="9">
         <v>0</v>
       </c>
       <c r="T14" s="9">
-        <v>0</v>
+        <v>-1373254</v>
       </c>
       <c r="U14" s="9">
         <v>0</v>
       </c>
       <c r="V14" s="9">
-        <v>-6654308</v>
+        <v>-5281054</v>
       </c>
       <c r="W14" s="9">
         <v>-23857</v>
@@ -1662,8 +1662,16 @@
       <c r="X14" s="9">
         <v>-3866234</v>
       </c>
+      <c r="Y14" s="11">
+        <f>SUM(H14:J14)</f>
+        <v>-6613784</v>
+      </c>
+      <c r="AC14" s="11">
+        <f>SUM(L14:N14)</f>
+        <v>-2707852</v>
+      </c>
     </row>
-    <row r="15" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>48</v>
       </c>
@@ -1737,7 +1745,7 @@
         <v>-29639</v>
       </c>
     </row>
-    <row r="16" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>29</v>
       </c>
@@ -1811,7 +1819,7 @@
         <v>-583203</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
@@ -1885,7 +1893,7 @@
         <v>-214819</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>28</v>
       </c>
@@ -1959,7 +1967,7 @@
         <v>-579057</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>49</v>
       </c>
@@ -2033,7 +2041,7 @@
         <v>-40415</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>30</v>
       </c>
@@ -2107,7 +2115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>31</v>
       </c>
@@ -2181,7 +2189,7 @@
         <v>-823997</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
@@ -2255,7 +2263,7 @@
         <v>-5204665</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>35</v>
       </c>
@@ -2329,7 +2337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>40</v>
       </c>
@@ -2403,7 +2411,7 @@
         <v>-97640</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>42</v>
       </c>
@@ -2477,7 +2485,7 @@
         <v>-216628</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>45</v>
       </c>
@@ -2551,7 +2559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>46</v>
       </c>
@@ -2625,7 +2633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>50</v>
       </c>
